--- a/events/Prague_2017_WC/Prague_2017_WC_start.xlsx
+++ b/events/Prague_2017_WC/Prague_2017_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W709"/>
+  <dimension ref="A1:AC709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1413,12 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -1451,12 +1481,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -1519,12 +1549,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -1587,12 +1617,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -1655,12 +1685,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -1723,12 +1753,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -1791,12 +1821,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -1859,12 +1889,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -1927,12 +1957,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -1995,12 +2025,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -2063,12 +2093,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -2131,12 +2161,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -2199,12 +2229,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -2267,12 +2297,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -2335,12 +2365,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -2398,7 +2428,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -2456,7 +2486,7 @@
           <t>SHRIVASTAVA Jahanvi</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>68935</t>
         </is>
@@ -2567,7 +2597,7 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -2625,7 +2655,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -2736,7 +2766,7 @@
           <t>YU Cuishan</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>75380</t>
         </is>
@@ -2794,7 +2824,7 @@
           <t>JELENSKA Oliwia</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>75730</t>
         </is>
@@ -2852,7 +2882,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -2910,7 +2940,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -2968,7 +2998,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -3079,7 +3109,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -3137,7 +3167,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -3195,7 +3225,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -3253,7 +3283,7 @@
           <t>HURKALA Ewa</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>43976</t>
         </is>
@@ -3311,7 +3341,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -3369,7 +3399,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -3427,7 +3457,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -3538,7 +3568,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -3596,7 +3626,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -3760,7 +3790,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -3818,7 +3848,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -3876,7 +3906,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -3987,7 +4017,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -4045,7 +4075,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -4103,7 +4133,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -4161,7 +4191,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -4219,7 +4249,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -4277,7 +4307,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -4335,7 +4365,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -4393,7 +4423,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -4451,7 +4481,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -4509,7 +4539,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -4567,7 +4597,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -4625,7 +4655,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -4736,7 +4766,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -4794,7 +4824,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -4852,7 +4882,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -4910,7 +4940,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -4968,7 +4998,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -5079,7 +5109,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -5137,7 +5167,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -5195,7 +5225,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -5253,7 +5283,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -5311,7 +5341,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -5369,7 +5399,7 @@
           <t>VERMA Dharmendra</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>75387</t>
         </is>
@@ -5427,7 +5457,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -5485,7 +5515,7 @@
           <t>KEER Kuldeep Singh</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>68932</t>
         </is>
@@ -5543,7 +5573,7 @@
           <t>KEER Dheeraj</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>68963</t>
         </is>
@@ -5601,7 +5631,7 @@
           <t>WU Shao-Hsuan</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>43104</t>
         </is>
@@ -5659,7 +5689,7 @@
           <t>RODRIGUES Guilherme</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>60486</t>
         </is>
@@ -5717,7 +5747,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -5775,7 +5805,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -5833,7 +5863,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -5891,7 +5921,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -5949,7 +5979,7 @@
           <t>OULHEN Pol</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>51932</t>
         </is>
@@ -6007,7 +6037,7 @@
           <t>MUSGRAVE Andrew</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>60102</t>
         </is>
@@ -6065,7 +6095,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -6123,7 +6153,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -6181,7 +6211,7 @@
           <t>LEE Han-Cheng</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
@@ -6239,7 +6269,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -6297,7 +6327,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -6355,7 +6385,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -6413,7 +6443,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -6471,7 +6501,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -6529,7 +6559,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -6587,7 +6617,7 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -6645,7 +6675,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -6756,7 +6786,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -6814,7 +6844,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -6872,7 +6902,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -6930,7 +6960,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -6988,7 +7018,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -7046,7 +7076,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -7104,7 +7134,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -7162,7 +7192,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -7220,7 +7250,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -7278,7 +7308,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -7336,7 +7366,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -7394,7 +7424,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -7452,7 +7482,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -7510,7 +7540,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -7568,7 +7598,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -7626,7 +7656,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -7684,7 +7714,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -7742,7 +7772,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -7853,7 +7883,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -7911,7 +7941,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -7969,7 +7999,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -8027,7 +8057,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -8085,7 +8115,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -8143,7 +8173,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -8201,7 +8231,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -8259,7 +8289,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -8317,7 +8347,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -8428,7 +8458,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -8486,7 +8516,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -8544,7 +8574,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -8602,7 +8632,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -8660,7 +8690,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -8718,7 +8748,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -8776,7 +8806,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -8834,7 +8864,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -8892,7 +8922,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -8950,7 +8980,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -9008,7 +9038,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -9066,7 +9096,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -9124,7 +9154,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -9182,7 +9212,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -9240,7 +9270,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -9298,7 +9328,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -9356,7 +9386,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -9414,7 +9444,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -9472,7 +9502,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -9530,7 +9560,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -9588,7 +9618,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -9646,7 +9676,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -9704,7 +9734,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -9762,7 +9792,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -9820,7 +9850,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -9878,7 +9908,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -9936,7 +9966,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -9994,7 +10024,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -10052,7 +10082,7 @@
           <t>SHRIVASTAVA Jahanvi</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>68935</t>
         </is>
@@ -10163,7 +10193,7 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -10221,7 +10251,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -10279,7 +10309,7 @@
           <t>RAO Jhih-Syuan</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
@@ -10337,7 +10367,7 @@
           <t>YU Cuishan</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>75380</t>
         </is>
@@ -10395,7 +10425,7 @@
           <t>JELENSKA Oliwia</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>75730</t>
         </is>
@@ -10453,7 +10483,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -10511,7 +10541,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -10569,7 +10599,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -10627,7 +10657,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -10685,7 +10715,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -10743,7 +10773,7 @@
           <t>HURKALA Ewa</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>43976</t>
         </is>
@@ -10801,7 +10831,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -10912,7 +10942,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -10970,7 +11000,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -11134,7 +11164,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -11192,7 +11222,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -11303,7 +11333,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -11361,7 +11391,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -11419,7 +11449,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -11477,7 +11507,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -11535,7 +11565,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -11593,7 +11623,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -11651,7 +11681,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -11709,7 +11739,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -11820,7 +11850,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -11878,7 +11908,7 @@
           <t>VERMA Dharmendra</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>75387</t>
         </is>
@@ -11936,7 +11966,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -11994,7 +12024,7 @@
           <t>KEER Kuldeep Singh</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>68932</t>
         </is>
@@ -12052,7 +12082,7 @@
           <t>KEER Dheeraj</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>68963</t>
         </is>
@@ -12110,7 +12140,7 @@
           <t>WU Shao-Hsuan</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>43104</t>
         </is>
@@ -12168,7 +12198,7 @@
           <t>RODRIGUES Guilherme</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>60486</t>
         </is>
@@ -12226,7 +12256,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -12284,7 +12314,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -12342,7 +12372,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -12400,7 +12430,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -12458,7 +12488,7 @@
           <t>OULHEN Pol</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>51932</t>
         </is>
@@ -12516,7 +12546,7 @@
           <t>MUSGRAVE Andrew</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>60102</t>
         </is>
@@ -12574,7 +12604,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -12632,7 +12662,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -12690,7 +12720,7 @@
           <t>LEE Han-Cheng</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
@@ -12748,7 +12778,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -12806,7 +12836,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -12864,7 +12894,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -12922,7 +12952,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -12980,7 +13010,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -13038,7 +13068,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -13096,7 +13126,7 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -13207,7 +13237,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -13265,7 +13295,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -13323,7 +13353,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -13381,7 +13411,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -13439,7 +13469,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -13497,7 +13527,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -13555,7 +13585,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -13613,7 +13643,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -13671,7 +13701,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -13729,7 +13759,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -13787,7 +13817,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -13845,7 +13875,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -13903,7 +13933,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -13961,7 +13991,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -14019,7 +14049,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -14130,7 +14160,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -14188,7 +14218,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -14246,7 +14276,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -14304,7 +14334,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -14362,7 +14392,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -14420,7 +14450,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -14531,7 +14561,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -14589,7 +14619,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -14647,7 +14677,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -14705,7 +14735,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -15081,12 +15111,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>37268</t>
         </is>
       </c>
-      <c r="V254" t="inlineStr">
+      <c r="Y254" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -15149,12 +15179,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V255" t="inlineStr">
+      <c r="Y255" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -15217,7 +15247,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V256" t="inlineStr">
+      <c r="Y256" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -15280,12 +15310,12 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
+      <c r="Y257" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -15343,7 +15373,7 @@
           <t>POLAT Gamze</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>71755</t>
         </is>
@@ -15401,7 +15431,7 @@
           <t>DHURWE Ganeshvri</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>68934</t>
         </is>
@@ -15459,7 +15489,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -15517,7 +15547,7 @@
           <t>PANDEY Aarti</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>68936</t>
         </is>
@@ -15628,7 +15658,7 @@
           <t>CHANG Chu-Han</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>51896</t>
         </is>
@@ -15686,7 +15716,7 @@
           <t>FLEPP Milena</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>73274</t>
         </is>
@@ -15744,7 +15774,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -15802,7 +15832,7 @@
           <t>HUVELIN Flora</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>51787</t>
         </is>
@@ -15860,7 +15890,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -15918,7 +15948,7 @@
           <t>MOUFFLE Lisa</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>65746</t>
         </is>
@@ -15976,7 +16006,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -16034,7 +16064,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -16092,7 +16122,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -16150,7 +16180,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -16208,7 +16238,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -16266,7 +16296,7 @@
           <t>KONDRATENKO Xeniya</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>42152</t>
         </is>
@@ -16324,7 +16354,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -16382,7 +16412,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -16440,7 +16470,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -16498,7 +16528,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -16556,7 +16586,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -16667,7 +16697,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -16725,7 +16755,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -16783,7 +16813,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -16841,7 +16871,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -16899,7 +16929,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -16957,7 +16987,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -17015,7 +17045,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -17073,7 +17103,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -17131,7 +17161,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -17189,7 +17219,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -17247,7 +17277,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -17305,7 +17335,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -17363,7 +17393,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -17421,7 +17451,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -17479,7 +17509,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -17537,7 +17567,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -17595,7 +17625,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -17653,7 +17683,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -17711,7 +17741,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -17769,7 +17799,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -17827,7 +17857,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -17885,7 +17915,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -17943,7 +17973,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -18001,7 +18031,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -18059,7 +18089,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -18117,7 +18147,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -18175,7 +18205,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -18233,7 +18263,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -18291,7 +18321,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -18349,7 +18379,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -18407,7 +18437,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -18465,7 +18495,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -18523,7 +18553,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -18581,7 +18611,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -18639,7 +18669,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -18697,7 +18727,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -18755,7 +18785,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -18813,7 +18843,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -18871,7 +18901,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -18929,7 +18959,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -18987,7 +19017,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -19045,7 +19075,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -19103,7 +19133,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -19161,7 +19191,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -19219,7 +19249,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -19277,7 +19307,7 @@
           <t>CIFTCI Murat</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>43512</t>
         </is>
@@ -19335,7 +19365,7 @@
           <t>BATHAM Virendra</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>68965</t>
         </is>
@@ -19393,7 +19423,7 @@
           <t>PARMAR Prince</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
@@ -19451,7 +19481,7 @@
           <t>SHKLIARUK Nikolay</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -19509,7 +19539,7 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -19567,7 +19597,7 @@
           <t>CHANG Yun-Chuan</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>37002</t>
         </is>
@@ -19625,7 +19655,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -19683,7 +19713,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -19741,7 +19771,7 @@
           <t>ROISIN Lucas</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>55580</t>
         </is>
@@ -19799,7 +19829,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -19857,7 +19887,7 @@
           <t>REN Qinkang</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>75438</t>
         </is>
@@ -19968,7 +19998,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -20026,7 +20056,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -20084,7 +20114,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -20142,7 +20172,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -20200,7 +20230,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -20258,7 +20288,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -20316,7 +20346,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -20374,7 +20404,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -20432,7 +20462,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -20490,7 +20520,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -20548,7 +20578,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -20606,7 +20636,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -20664,7 +20694,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -20722,7 +20752,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -20780,7 +20810,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -20838,7 +20868,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -20896,7 +20926,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -20954,7 +20984,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -21012,7 +21042,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -21070,7 +21100,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -21128,7 +21158,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -21186,7 +21216,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -21244,7 +21274,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -21302,7 +21332,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -21360,7 +21390,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -21418,7 +21448,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -21476,7 +21506,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -21534,7 +21564,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -21592,7 +21622,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -21650,7 +21680,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -21708,7 +21738,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -21766,7 +21796,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -21824,7 +21854,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -21882,7 +21912,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -21940,7 +21970,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -21998,7 +22028,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -22056,7 +22086,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -22114,7 +22144,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -22172,7 +22202,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -22230,7 +22260,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -22288,7 +22318,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -22346,7 +22376,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -22404,7 +22434,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -22462,7 +22492,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -22520,7 +22550,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -22578,7 +22608,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -22636,7 +22666,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -22694,7 +22724,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -22752,7 +22782,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -22810,7 +22840,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -22868,7 +22898,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -22926,7 +22956,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -22984,7 +23014,7 @@
           <t>POLAT Gamze</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>71755</t>
         </is>
@@ -23042,7 +23072,7 @@
           <t>DHURWE Ganeshvri</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>68934</t>
         </is>
@@ -23100,7 +23130,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -23158,7 +23188,7 @@
           <t>PANDEY Aarti</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>68936</t>
         </is>
@@ -23269,7 +23299,7 @@
           <t>CHANG Chu-Han</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>51896</t>
         </is>
@@ -23327,7 +23357,7 @@
           <t>FLEPP Milena</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>73274</t>
         </is>
@@ -23385,7 +23415,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -23443,7 +23473,7 @@
           <t>HUVELIN Flora</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>51787</t>
         </is>
@@ -23501,7 +23531,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -23559,7 +23589,7 @@
           <t>MOUFFLE Lisa</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>65746</t>
         </is>
@@ -23617,7 +23647,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -23675,7 +23705,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -23733,7 +23763,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -23791,7 +23821,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -23849,7 +23879,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -23907,7 +23937,7 @@
           <t>KONDRATENKO Xeniya</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>42152</t>
         </is>
@@ -23965,7 +23995,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -24023,7 +24053,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -24081,7 +24111,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -24139,7 +24169,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -24197,7 +24227,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -24308,7 +24338,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -24366,7 +24396,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -24424,7 +24454,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -24482,7 +24512,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -24540,7 +24570,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -24598,7 +24628,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -24656,7 +24686,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -24714,7 +24744,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -24772,7 +24802,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -24830,7 +24860,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -24888,7 +24918,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -24946,7 +24976,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -25004,7 +25034,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -25062,7 +25092,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -25120,7 +25150,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -25178,7 +25208,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -25236,7 +25266,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -25294,7 +25324,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -25352,7 +25382,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -25410,7 +25440,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -25468,7 +25498,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -25526,7 +25556,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -25584,7 +25614,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -25642,7 +25672,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -25700,7 +25730,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -25758,7 +25788,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -25816,7 +25846,7 @@
           <t>CIFTCI Murat</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>43512</t>
         </is>
@@ -25874,7 +25904,7 @@
           <t>BATHAM Virendra</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>68965</t>
         </is>
@@ -25932,7 +25962,7 @@
           <t>PARMAR Prince</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
@@ -25990,7 +26020,7 @@
           <t>SHKLIARUK Nikolay</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -26048,7 +26078,7 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -26106,7 +26136,7 @@
           <t>CHANG Yun-Chuan</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>37002</t>
         </is>
@@ -26164,7 +26194,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -26222,7 +26252,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -26280,7 +26310,7 @@
           <t>ROISIN Lucas</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>55580</t>
         </is>
@@ -26338,7 +26368,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -26396,7 +26426,7 @@
           <t>REN Qinkang</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>75438</t>
         </is>
@@ -26507,7 +26537,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -26565,7 +26595,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -26623,7 +26653,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -26681,7 +26711,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -26739,7 +26769,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -26797,7 +26827,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -26855,7 +26885,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -26913,7 +26943,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -26971,7 +27001,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -27029,7 +27059,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -27087,7 +27117,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -27145,7 +27175,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -27203,7 +27233,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -27261,7 +27291,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -27319,7 +27349,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -27377,7 +27407,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -27435,7 +27465,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -27493,7 +27523,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -27551,7 +27581,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -27609,7 +27639,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -27667,7 +27697,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -27725,7 +27755,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -27783,7 +27813,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -27841,7 +27871,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -27899,7 +27929,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -27957,7 +27987,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -28015,7 +28045,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -28073,7 +28103,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -28131,7 +28161,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -28189,7 +28219,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -28247,7 +28277,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -28305,7 +28335,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -28363,7 +28393,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -29219,12 +29249,12 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V500" t="inlineStr">
+      <c r="Y500" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -29287,12 +29317,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V501" t="inlineStr">
+      <c r="Y501" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -29355,12 +29385,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V502" t="inlineStr">
+      <c r="Y502" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -29423,12 +29453,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V503" t="inlineStr">
+      <c r="Y503" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -29491,12 +29521,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V504" t="inlineStr">
+      <c r="Y504" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -29559,12 +29589,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V505" t="inlineStr">
+      <c r="Y505" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -29627,12 +29657,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V506" t="inlineStr">
+      <c r="Y506" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -29695,12 +29725,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V507" t="inlineStr">
+      <c r="Y507" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -29763,12 +29793,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V508" t="inlineStr">
+      <c r="Y508" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -29831,12 +29861,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V509" t="inlineStr">
+      <c r="Y509" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -29899,12 +29929,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V510" t="inlineStr">
+      <c r="Y510" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -29967,12 +29997,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V511" t="inlineStr">
+      <c r="Y511" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -30035,12 +30065,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V512" t="inlineStr">
+      <c r="Y512" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -30103,12 +30133,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V513" t="inlineStr">
+      <c r="Y513" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -30171,12 +30201,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V514" t="inlineStr">
+      <c r="Y514" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -30234,7 +30264,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -30345,7 +30375,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -30456,7 +30486,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -30514,7 +30544,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -30572,7 +30602,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -30630,7 +30660,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -30688,7 +30718,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30746,7 +30776,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -30804,7 +30834,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -30862,7 +30892,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -30920,7 +30950,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -30978,7 +31008,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -31036,7 +31066,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -31147,7 +31177,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -31205,7 +31235,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -31263,7 +31293,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -31321,7 +31351,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -31379,7 +31409,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -31490,7 +31520,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -31548,7 +31578,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -31606,7 +31636,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -31664,7 +31694,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -31722,7 +31752,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -31780,7 +31810,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -31838,7 +31868,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -31896,7 +31926,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -31954,7 +31984,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -32012,7 +32042,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -32070,7 +32100,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -32128,7 +32158,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -32186,7 +32216,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -32244,7 +32274,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -32302,7 +32332,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -32413,7 +32443,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -32524,7 +32554,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -32582,7 +32612,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -32640,7 +32670,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -32698,7 +32728,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -32756,7 +32786,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -32814,7 +32844,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -32872,7 +32902,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -32930,7 +32960,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -32988,7 +33018,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -33046,7 +33076,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -33104,7 +33134,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -33162,7 +33192,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -33220,7 +33250,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -33278,7 +33308,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -33336,7 +33366,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -33394,7 +33424,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -33452,7 +33482,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -33510,7 +33540,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -33568,7 +33598,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -33626,7 +33656,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -33684,7 +33714,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -33742,7 +33772,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -33800,7 +33830,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -33858,7 +33888,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -33916,7 +33946,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -33974,7 +34004,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -34032,7 +34062,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -34090,7 +34120,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -34148,7 +34178,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -34206,7 +34236,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -34279,12 +34309,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V585" t="inlineStr">
+      <c r="Y585" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -34357,12 +34387,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V586" t="inlineStr">
+      <c r="Y586" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -34435,12 +34465,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V587" t="inlineStr">
+      <c r="Y587" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -34513,12 +34543,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V588" t="inlineStr">
+      <c r="Y588" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -34591,12 +34621,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V589" t="inlineStr">
+      <c r="Y589" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -34669,12 +34699,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V590" t="inlineStr">
+      <c r="Y590" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -34747,12 +34777,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V591" t="inlineStr">
+      <c r="Y591" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -34825,12 +34855,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V592" t="inlineStr">
+      <c r="Y592" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -34903,12 +34933,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V593" t="inlineStr">
+      <c r="Y593" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -34981,12 +35011,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V594" t="inlineStr">
+      <c r="Y594" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -35054,7 +35084,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -35122,7 +35152,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -35190,7 +35220,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -35258,7 +35288,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -35326,7 +35356,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -35394,7 +35424,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -35462,7 +35492,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -35530,7 +35560,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -35661,7 +35691,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -35729,7 +35759,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -35797,7 +35827,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -35865,7 +35895,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -35933,7 +35963,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -36001,7 +36031,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -36069,7 +36099,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -36137,7 +36167,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -36205,7 +36235,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -36273,7 +36303,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -36341,7 +36371,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -36722,12 +36752,12 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V621" t="inlineStr">
+      <c r="Y621" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -36790,12 +36820,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>37268</t>
         </is>
       </c>
-      <c r="V622" t="inlineStr">
+      <c r="Y622" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -36858,12 +36888,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V623" t="inlineStr">
+      <c r="Y623" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -36926,7 +36956,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V624" t="inlineStr">
+      <c r="Y624" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -36984,7 +37014,7 @@
           <t>MOUFFLE Lisa</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>65746</t>
         </is>
@@ -37042,7 +37072,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -37100,7 +37130,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -37158,7 +37188,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -37216,7 +37246,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -37274,7 +37304,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -37332,7 +37362,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -37390,7 +37420,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -37448,7 +37478,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -37506,7 +37536,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -37564,7 +37594,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -37622,7 +37652,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -37680,7 +37710,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -37738,7 +37768,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -37796,7 +37826,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -37854,7 +37884,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -37912,7 +37942,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -37970,7 +38000,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -38028,7 +38058,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -38086,7 +38116,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -38144,7 +38174,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -38202,7 +38232,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -38260,7 +38290,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -38318,7 +38348,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -38376,7 +38406,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -38434,7 +38464,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -38492,7 +38522,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -38550,7 +38580,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -38608,7 +38638,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -38666,7 +38696,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -38724,7 +38754,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -38782,7 +38812,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -38840,7 +38870,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -38898,7 +38928,7 @@
           <t>ROISIN Lucas</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>55580</t>
         </is>
@@ -38956,7 +38986,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -39014,7 +39044,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -39072,7 +39102,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -39130,7 +39160,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -39188,7 +39218,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -39246,7 +39276,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -39304,7 +39334,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -39362,7 +39392,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -39420,7 +39450,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -39478,7 +39508,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -39536,7 +39566,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -39594,7 +39624,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -39652,7 +39682,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -39710,7 +39740,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -39768,7 +39798,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -39826,7 +39856,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -39884,7 +39914,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U675" t="inlineStr">
+      <c r="X675" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -39942,7 +39972,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -40000,7 +40030,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U677" t="inlineStr">
+      <c r="X677" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -40058,7 +40088,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -40116,7 +40146,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -40174,7 +40204,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -40232,7 +40262,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -40290,7 +40320,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -40348,7 +40378,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -40406,7 +40436,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -40479,12 +40509,12 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
       </c>
-      <c r="V685" t="inlineStr">
+      <c r="Y685" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -40557,12 +40587,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
+      <c r="X686" t="inlineStr">
         <is>
           <t>37268</t>
         </is>
       </c>
-      <c r="V686" t="inlineStr">
+      <c r="Y686" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -40635,12 +40665,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V687" t="inlineStr">
+      <c r="Y687" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -40713,7 +40743,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V688" t="inlineStr">
+      <c r="Y688" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -40781,7 +40811,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -40849,7 +40879,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -40917,7 +40947,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -40985,7 +41015,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -41053,7 +41083,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -41121,7 +41151,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -41189,7 +41219,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -41257,7 +41287,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -41325,7 +41355,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -41393,7 +41423,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -41461,7 +41491,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -41529,7 +41559,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -41597,7 +41627,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -41665,7 +41695,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -41733,7 +41763,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -41801,7 +41831,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -41869,7 +41899,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -41937,7 +41967,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -42005,7 +42035,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -42073,7 +42103,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -42141,7 +42171,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
